--- a/Vulnerability Test Results/findings.xlsx
+++ b/Vulnerability Test Results/findings.xlsx
@@ -2079,7 +2079,7 @@
     <t>Assessment date</t>
   </si>
   <si>
-    <t>2026-08-27T05:22:03.511Z</t>
+    <t>2026-08-27T05:38:22.216Z</t>
   </si>
   <si>
     <t>Scope</t>
